--- a/artfynd/S 57-2026 artfynd.xlsx
+++ b/artfynd/S 57-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,8 +784,16 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74500094</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>